--- a/samples/template.xlsx
+++ b/samples/template.xlsx
@@ -1,60 +1,121 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <x:workbookPr codeName="ThisWorkbook"/>
+  <x:bookViews>
+    <x:workbookView firstSheet="0" activeTab="0"/>
+  </x:bookViews>
   <x:sheets>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_guide" sheetId="1" r:id="Redd281d8037c4f6c"/>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="setting" sheetId="2" r:id="R1dc7c92dad704ae6"/>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="root" sheetId="3" r:id="Rd150695fabe949c6"/>
   </x:sheets>
+  <x:definedNames/>
+  <x:calcPr calcId="125725"/>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:si>
-    <x:t xml:space="preserve">ExcelToJson 空ひな形</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">key</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">value</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">description</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">rootType</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">array</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">rootを単一objectまたはarrayとして出力します。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">emptyCell</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">omit</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">空セルのプロパティを出力しません。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">dateInputFormat</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">空欄の場合はCurrentCultureで解析します。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">dateOutputFormat</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">空欄の場合は既定のISO 8601形式で出力します。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ID</x:t>
+    <x:t>ExcelToJson 空ひな形</x:t>
+  </x:si>
+  <x:si>
+    <x:t>作業開始</x:t>
+  </x:si>
+  <x:si>
+    <x:t>このファイルを別名でコピーし、rootシートへ列とデータを追加してください。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>列</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A列はIDです。B列以降の1行目にJSONプロパティ名を入力します。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>型メモ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>B列以降のヘッダーへ旧式Excelメモを追加し、number、boolean、date、object:シート名、array:シート名、scalar-array:シート名を指定します。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>セル型上書き</x:t>
+  </x:si>
+  <x:si>
+    <x:t>データセルへ同じ書式の旧式Excelメモを追加すると、そのセルだけヘッダー型を上書きします。
+空または空白だけのメモは上書きしません。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>参照</x:t>
+  </x:si>
+  <x:si>
+    <x:t>object、array、scalar-arrayのセルには参照先シートのIDを入力します。参照先シートもA列をIDにします。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IDと参照IDは前後空白を除去し、大文字小文字を区別します。ID列はJSONへ出力されません。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>空行終端</x:t>
+  </x:si>
+  <x:si>
+    <x:t>データは2行目から入力します。全セルが空の行が現れると、その後の行は読み取られません。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>rootType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>初期値はarrayで、空のまま変換すると[]になります。objectはrootを1行、scalar-arrayはrootをIDとvalueの2列にします。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>scalar-array</x:t>
+  </x:si>
+  <x:si>
+    <x:t>参照先はIDとvalueの2列だけにし、valueのヘッダーメモでtext、number、boolean、dateを指定します。メモなしはtextです。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>詳細仕様</x:t>
+  </x:si>
+  <x:si>
+    <x:t>正確な入力規則はリポジトリのdocs/REQUIREMENTS.mdを参照してください。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>key</x:t>
+  </x:si>
+  <x:si>
+    <x:t>value</x:t>
+  </x:si>
+  <x:si>
+    <x:t>description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>array</x:t>
+  </x:si>
+  <x:si>
+    <x:t>rootを単一object、object配列、またはスカラー配列として出力します。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>emptyCell</x:t>
+  </x:si>
+  <x:si>
+    <x:t>omit</x:t>
+  </x:si>
+  <x:si>
+    <x:t>空セルのプロパティを出力しません。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dateInputFormat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>空欄の場合はCurrentCultureで解析します。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dateOutputFormat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>空欄の場合は既定のISO 8601形式で出力します。</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -151,7 +212,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="13">
+  <x:cellXfs count="14">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom" wrapText="0"/>
     </x:xf>
@@ -191,9 +252,14 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellXfs>
-  <x:cellStyles count="1">
+  <x:cellStyles count="2">
     <x:cellStyle name="Normal" xfId="0"/>
+    <x:cellStyle name="Normal" xfId="1" builtinId="0"/>
   </x:cellStyles>
 </x:styleSheet>
 </file>
@@ -411,180 +477,209 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="1" summaryRight="1"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:B12"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="18.71062469482422" customWidth="1"/>
-    <x:col min="2" max="2" width="68.71062469482422" customWidth="1"/>
+    <x:col min="1" max="1" width="18.710625" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="68.710625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="30" customHeight="1">
+    <x:row r="1" spans="1:2" ht="30" customHeight="1">
       <x:c r="A1" s="1" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
     </x:row>
-    <x:row r="3" ht="14.25" customHeight="1">
-      <x:c r="A3" s="2" t="str">
-        <x:v>作業開始</x:v>
-      </x:c>
-      <x:c r="B3" s="3" t="str">
-        <x:v>このファイルを別名でコピーし、rootシートへ列とデータを追加してください。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="14.25" customHeight="1">
-      <x:c r="A4" s="2" t="str">
-        <x:v>列</x:v>
-      </x:c>
-      <x:c r="B4" s="3" t="str">
-        <x:v>A列はIDです。B列以降の1行目にJSONプロパティ名を入力します。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="28.5" customHeight="1">
-      <x:c r="A5" s="2" t="str">
-        <x:v>型メモ</x:v>
-      </x:c>
-      <x:c r="B5" s="3" t="str">
-        <x:v>B列以降のヘッダーへ旧式Excelメモを追加し、number、boolean、date、object:シート名、array:シート名を指定します。
-メモがない、または空白だけのヘッダーはtextです。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="28.5" customHeight="1">
-      <x:c r="A6" s="2" t="str">
-        <x:v>セル型上書き</x:v>
-      </x:c>
-      <x:c r="B6" s="3" t="str">
-        <x:v>データセルへ同じ書式の旧式Excelメモを追加すると、そのセルだけヘッダー型を上書きします。
-空または空白だけのメモは上書きしません。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="14.25" customHeight="1">
-      <x:c r="A7" s="2" t="str">
-        <x:v>参照</x:v>
-      </x:c>
-      <x:c r="B7" s="3" t="str">
-        <x:v>objectまたはarrayのセルには参照先シートのIDを入力します。参照先シートもA列をIDにします。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="14.25" customHeight="1">
-      <x:c r="A8" s="2" t="str">
-        <x:v>ID</x:v>
-      </x:c>
-      <x:c r="B8" s="3" t="str">
-        <x:v>IDと参照IDは前後空白を除去し、大文字小文字を区別します。ID列はJSONへ出力されません。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="14.25" customHeight="1">
-      <x:c r="A9" s="2" t="str">
-        <x:v>空行終端</x:v>
-      </x:c>
-      <x:c r="B9" s="3" t="str">
-        <x:v>データは2行目から入力します。全セルが空の行が現れると、その後の行は読み取られません。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="28.5" customHeight="1">
-      <x:c r="A10" s="2" t="str">
-        <x:v>rootType</x:v>
-      </x:c>
-      <x:c r="B10" s="3" t="str">
-        <x:v>初期値はarrayで、空のまま変換すると[]になります。
-objectへ変更する場合はrootのデータ行をちょうど1行にしてください。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="14.25" customHeight="1">
-      <x:c r="A11" s="10" t="str">
-        <x:v>詳細仕様</x:v>
-      </x:c>
-      <x:c r="B11" s="12" t="str">
-        <x:v>正確な入力規則はリポジトリのdocs/REQUIREMENTS.mdを参照してください。</x:v>
+    <x:row r="3" spans="1:2" ht="14.25" customHeight="1">
+      <x:c r="A3" s="2" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B3" s="3" t="s">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:2" ht="14.25" customHeight="1">
+      <x:c r="A4" s="2" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B4" s="3" t="s">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:2" ht="28.5" customHeight="1">
+      <x:c r="A5" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B5" s="3" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:2" ht="28.5" customHeight="1">
+      <x:c r="A6" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B6" s="3" t="s">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:2" ht="30" customHeight="1">
+      <x:c r="A7" s="2" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B7" s="3" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:2" ht="14.25" customHeight="1">
+      <x:c r="A8" s="2" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B8" s="3" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:2" ht="14.25" customHeight="1">
+      <x:c r="A9" s="2" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B9" s="3" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:2" ht="28.5" customHeight="1">
+      <x:c r="A10" s="2" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B10" s="3" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:2" ht="42" customHeight="1">
+      <x:c r="A11" s="2" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B11" s="3" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:2" ht="14.25" customHeight="1">
+      <x:c r="A12" s="13" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B12" s="12" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:mergeCells>
+  <x:mergeCells count="1">
     <x:mergeCell ref="A1:B1"/>
   </x:mergeCells>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter/>
+  <x:tableParts count="0"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="1" summaryRight="1"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:C5"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="22.71062469482422" customWidth="1"/>
-    <x:col min="2" max="2" width="20.71062469482422" customWidth="1"/>
-    <x:col min="3" max="3" width="54.71062469482422" customWidth="1"/>
+    <x:col min="1" max="1" width="22.710625" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="20.710625" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="54.710625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="14.25" customHeight="1">
+    <x:row r="1" spans="1:3" ht="14.25" customHeight="1">
       <x:c r="A1" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B1" s="4" t="s">
-        <x:v>2</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C1" s="4" t="s">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" ht="14.25" customHeight="1">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:3" ht="14.25" customHeight="1">
       <x:c r="A2" s="5" t="s">
-        <x:v>4</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B2" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C2" s="6" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" ht="14.25" customHeight="1">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:3" ht="14.25" customHeight="1">
       <x:c r="A3" s="5" t="s">
-        <x:v>7</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B3" s="5" t="s">
-        <x:v>8</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C3" s="6" t="s">
-        <x:v>9</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="14.25" customHeight="1">
+        <x:v>28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:3" ht="14.25" customHeight="1">
       <x:c r="A4" s="5" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B4" s="5"/>
       <x:c r="C4" s="6" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="14.25" customHeight="1">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:3" ht="14.25" customHeight="1">
       <x:c r="A5" s="5" t="s">
-        <x:v>12</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B5" s="5"/>
       <x:c r="C5" s="6" t="s">
-        <x:v>13</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter/>
+  <x:tableParts count="0"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="1" summaryRight="1"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:A1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="12.710624694824219" customWidth="1"/>
+    <x:col min="1" max="1" width="12.710625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="23" customHeight="1">
+    <x:row r="1" spans="1:1" ht="23" customHeight="1">
       <x:c r="A1" s="4" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter/>
+  <x:tableParts count="0"/>
 </x:worksheet>
 </file>